--- a/bug/tensorflow_bug_list.xlsx
+++ b/bug/tensorflow_bug_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\zrk\SF\code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\2025\paper\二次修改重投\bug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D23347-64E1-4B7F-9340-316CA7F51EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5428BEA3-8529-4EF1-AE66-D68F4960BFD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9075" yWindow="4410" windowWidth="25965" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tensorflow" sheetId="3" r:id="rId1"/>
@@ -25,34 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="60">
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://github.com/tensorflow/tensorflow/issues/105297</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">https://github.com/tensorflow/tensorflow/issues/105367  </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://github.com/CodersAcademy006/tensorflow/pull/9</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="189">
   <si>
     <r>
       <rPr>
@@ -86,31 +59,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://github.com/tensorflow/tensorflow/issues/104854</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
       <t>https://github.com/tensorflow/tensorflow/issues/105292</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://github.com/tensorflow/tensorflow/issues/104876</t>
     </r>
   </si>
   <si>
@@ -282,12 +231,6 @@
     </r>
   </si>
   <si>
-    <t>Segmentation fault (core dumped)</t>
-  </si>
-  <si>
-    <t>Aborted (core dumped)</t>
-  </si>
-  <si>
     <t>tf..assign_add</t>
   </si>
   <si>
@@ -328,9 +271,6 @@
   </si>
   <si>
     <t>tf.compat.v1.raw_ops.SparseMatrixSparseCholesky</t>
-  </si>
-  <si>
-    <t>double free</t>
   </si>
   <si>
     <t>tf.data.Dataset.batch</t>
@@ -398,23 +338,696 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
-    <t>Confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INTERNAL ASSERT FAILED</t>
-  </si>
-  <si>
     <t>Memory Leak</t>
+  </si>
+  <si>
+    <t>API Name</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Issue Link</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bug Type</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Status</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/tensorflow/tensorflow/issues/105367  </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/pull/105368
+https://github.com/CodersAcademy006/tensorflow/pull/9</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/pull/105369</t>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/pull/105345
+https://github.com/tensorflow/tensorflow/pull/106123
+https://github.com/tensorflow/tensorflow/pull/121708</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/issues/105297</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/pull/105631
+https://github.com/tensorflow/tensorflow/pull/105640</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/pull/105347
+https://github.com/tensorflow/tensorflow/pull/123102</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/issues/104876</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/pull/105285</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/pull/105290</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/issues/104854</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/tensorflow/tensorflow/pull/117891</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heap Buffer Overflow</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Segfault</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> INTERNAL ASSERT FAILURE</t>
+  </si>
+  <si>
+    <t>Aborted</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Segfault</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crash</t>
+  </si>
+  <si>
+    <t>OOM</t>
+  </si>
+  <si>
+    <t>New &amp; Confirmed</t>
+  </si>
+  <si>
+    <t>fixed commit</t>
+  </si>
+  <si>
+    <t>Trigger Conditions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Confirmation Date</t>
+  </si>
+  <si>
+    <t>Lib Version</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deduplication</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Minimal Reproducer</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maintainer Response</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Combining complex64 variables with tf.raw_ops.Conj and Variable.assign_add() on CPU/GPU; input is a complex64 tensor with non-zero imaginary parts.</t>
+  </si>
+  <si>
+    <t>Maintainers acknowledged the issue and marked it for community contributions. One user claimed to have a fix, and another confirmed the issue was resolved in TensorFlow 2.21, suggesting it was fixed in a later version.</t>
+  </si>
+  <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.17</t>
+  </si>
+  <si>
+    <t>No duplicates found</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+input_data = tf.constant([1 + 2j, 3 + 4j], dtype=tf.complex64)
+var = tf.Variable(input_data, dtype=tf.complex64)
+conj_result = tf.raw_ops.Conj(input=input_data)
+assign_add_op = var.assign_add(conj_result)</t>
+  </si>
+  <si>
+    <t>Using tf.get_variable() with dtype=tf.complex128 and initializer=tf.constant_initializer() containing complex numbers (e.g., [1.0+1.0j, 2.0+2.0j, 3.0+3.0j]) in TensorFlow 1.x compatibility mode. Reproduced on TensorFlow 2.17.</t>
+  </si>
+  <si>
+    <t>The maintainers acknowledged the issue but did not prioritize it for immediate fix. They marked it for community contributions and suggested users submit a PR. Later, a user reported that the issue could not be reproduced in TensorFlow 2.21, implying it may have been resolved in newer versions.</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>import tensorflow.compat.v1 as tf
+tf.get_variable("ref", shape=[3], dtype=tf.complex128, initializer=tf.constant_initializer([1.0+1.0j, 2.0+2.0j, 3.0+3.0j]))</t>
+  </si>
+  <si>
+    <t>Calling tf.raw_ops.TensorListSetItem with index=9223372036854775807 (INT64_MAX), resize_if_index_out_of_bounds=True, element_dtype=tf.float32, element_shape=[2], and input tensor list created with EmptyTensorList. Triggered on CPU/GPU with any system memory configuration due to excessive memory allocation attempt.</t>
+  </si>
+  <si>
+    <t>Maintainers acknowledged the issue and reproduced it, but marked it as not prioritized and opened for community contributions. They encouraged users to submit a PR with a fix and provided guidelines for contribution.</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+input_handle = tf.raw_ops.EmptyTensorList(element_dtype=tf.float32, element_shape=tf.TensorShape([2]), max_num_elements=5)
+index = tf.constant(9223372036854775807, dtype=tf.int32)
+item = tf.constant([1.0, 2.0], dtype=tf.float32)
+output_handle = tf.raw_ops.TensorListSetItem(input_handle=input_handle, index=index, item=item, resize_if_index_out_of_bounds=True, name='SetItem')</t>
+  </si>
+  <si>
+    <t>Setting intra_op_parallelism_threads to INT_MAX (2147483647) while creating a local TensorFlow server via tf.distribute.Server.create_local_server with config containing device_count={'GPU': 0}, inter_op_parallelism_threads=4, allow_soft_placement=True, log_device_placement=False. Occurs on CPU-only configuration.</t>
+  </si>
+  <si>
+    <t>Maintainers acknowledged the issue and marked it as 'contribution welcome'. They stated the request is not currently prioritized and encouraged community contributions. They requested contributors to fork the repo and submit a PR with a link to this issue for review.</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+config = tf.compat.v1.ConfigProto(device_count={'GPU': 0},
+    inter_op_parallelism_threads=4, intra_op_parallelism_threads=2147483647,
+    allow_soft_placement=True, log_device_placement=False)
+start = True
+server = tf.distribute.Server.create_local_server(config=config, start=start)</t>
+  </si>
+  <si>
+    <t>Using tf.raw_ops.AsString with width=2147483647 (INT_MAX), scientific=True, precision=2, shortest=False, fill='0', on GPU-enabled environment. The crash occurs after GPU device initialization.</t>
+  </si>
+  <si>
+    <t>Maintainers confirmed the issue occurs on tf-nightly and 2.21.0rc0. They marked it as not prioritized and opened for community contributions, encouraging users to submit a PR. One user commented they are investigating the root cause in as_string_op.cc and plan to submit a fix.</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+input_data = tf.constant([3.1415926, 2.71828], dtype=tf.float32)
+result = tf.raw_ops.AsString(input=input_data, precision=2, scientific=True, shortest=False, width=2147483647, fill='0', name='asString')</t>
+  </si>
+  <si>
+    <t>Calling tf.raw_ops.GatherV2 with a 2D tensor and an invalid axis parameter (axis=9), on a GPU-enabled system with CUDA. The crash occurs during CUDA device context initialization due to out-of-memory error, even though the axis value is out of bounds and should trigger an InvalidArgumentError.</t>
+  </si>
+  <si>
+    <t>Maintainer acknowledged the issue and confirmed that in TensorFlow 2.21, the correct behavior is to raise an InvalidArgumentError instead of crashing. They provided a Colab gist demonstrating the fixed behavior and noted the issue was not prioritized for immediate fix in 2.17, encouraging community contributions.</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+resource = tf.Variable([[1, 2, 3], [4, 5, 6]], dtype=tf.int32)
+indices = tf.constant([0, 1], dtype=tf.int32)
+dtype = tf.int32
+batch_dims = 0
+output = tf.raw_ops.GatherV2(params=resource, indices=indices, axis=9, batch_dims=batch_dims)</t>
+  </si>
+  <si>
+    <t>Large tensor dimensions: input shape [10, 10, 10, 10, 10], filters shape [3, 3, 3, 3, 5], strides [1, 2, 2, 2, 1], padding 'SAME', data_format 'NDHWC', on GPU-enabled system with CUDA. The bug triggers during GPU-to-CPU memory copy with invalid resource handles or out-of-memory conditions.</t>
+  </si>
+  <si>
+    <t>Maintainers acknowledged the issue and marked it for community contributions. One user claimed a fix in PR #105290. Later, another user could not reproduce the crash in TensorFlow 2.21, observing an InvalidArgumentError instead, suggesting the issue may have been resolved or changed behavior.</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+input_data = tf.random.uniform([10, 10, 10, 10, 10], minval=0, maxval=1, dtype=tf.float32)
+filters_data = tf.random.uniform([3, 3, 3, 3, 5], minval=0, maxval=1, dtype=tf.float32)
+strides_data = [1, 2, 2, 2, 1]
+padding_data = 'SAME'
+data_format_data = 'NDHWC'
+dilations_data = [1, 1, 1, 1, 1]
+name_data = 'conv3d_op'
+output = tf.nn.conv3d(input=input_data, filters=filters_data, strides=strides_data, padding=padding_data, data_format=data_format_data, dilations=dilations_data, name=name_data)</t>
+  </si>
+  <si>
+    <t>Using extremely large fft_length values (36028797018963968) on GPU with complex64 input data, triggering GPU memory exhaustion and cuFFT batched plan failure. The bug occurs in multi-GPU environments and is triggered by the combination of large FFT dimensions and limited GPU memory.</t>
+  </si>
+  <si>
+    <t>The maintainer acknowledged the issue but marked it as not prioritized and suggested community contributions. Later, another user tested the code on TensorFlow 2.21 in Colab and reported no issue, suggesting the problem may be environment-specific or resolved in newer versions.</t>
+  </si>
+  <si>
+    <t>2025-11-21</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.10</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+input_data = tf.constant([[1.0 + 1.0j, 2.0 + 2.0j], [3.0 + 3.0j, 4.0 + 4.0j]], dtype=tf.complex64)
+fft_length = tf.constant([36028797018963968, 36028797018963968], dtype=tf.int32)
+axes = tf.constant([0, 1], dtype=tf.int32)
+result = tf.signal.fft2d(input_data)
+# Expected: FFT result or graceful error
+# Actual: GPU memory exhaustion, cuFFT plan failure, core dump</t>
+  </si>
+  <si>
+    <t>Using an extremely large negative value (-36028797018963968) for the 'summarize' parameter in tf.debugging.assert_less on a GPU-enabled system, triggering GPU memory allocation failure, invalid CUDA handles, and GPU-&gt;CPU memcpy errors leading to core dump.</t>
+  </si>
+  <si>
+    <t>Maintainers acknowledged the issue but marked it as not prioritized and opened for community contributions. One maintainer later reported inability to reproduce the issue on TensorFlow 2.21, suggesting possible resolution or environmental dependency.</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+x = tf.constant([1, 2, 3], dtype=tf.float32)
+y = tf.constant([4, 5, 6], dtype=tf.float32)
+tf.debugging.assert_less(x, y, message='x should be less than y', summarize=-36028797018963968, name='assert_less_check')</t>
+  </si>
+  <si>
+    <t>Multi-GPU system with NVIDIA GPUs (compute capability 7.5 &amp; 8.6), during cuSolverDN library initialization in tf.raw_ops.Lu operation. Intermittent and probabilistic failure, not consistently reproducible. Occurs during GpuSolver handles creation.</t>
+  </si>
+  <si>
+    <t>The maintainers acknowledged the issue but marked it as low priority for community contributions. Later, a maintainer attempted to reproduce the issue on tf-nightly in Colab and could not reproduce it, suggesting the issue may have been resolved in newer versions. The issue was closed due to inactivity after being marked stale.</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+input_data = tf.constant([[4.0, 3.0], [6.0, 3.0]], dtype=tf.float32)
+lu, p = tf.raw_ops.Lu(input=input_data, output_idx_type=tf.int32, name='txt')</t>
+  </si>
+  <si>
+    <t>When calling tf.raw_ops.ResourceApplyAdagradV2 with resource variables (var, accum) of dtype float32 and hyperparameters (lr, epsilon, grad) of dtype float64. Occurs on GPU environments (e.g., NVIDIA RTX A6000, A100) and is reproducible in both CPU and GPU modes. The crash is triggered by a dtype mismatch during tensor validation in TensorFlow's core framework.</t>
+  </si>
+  <si>
+    <t>Maintainers acknowledged the issue and confirmed reproduction on TensorFlow 2.19.0 and 2.20.0. They marked it as 'contribution welcome' and stated it is not currently prioritized, encouraging community contributions. One contributor expressed interest in investigating the issue.</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.17.0, 2.19.0, 2.20.0</t>
+  </si>
+  <si>
+    <t>import numpy as np
+import tensorflow as tf
+np.random.seed(0)
+tf.random.set_seed(0)
+var = tf.Variable(np.random.rand(3), dtype=tf.float32)
+accum = tf.Variable(np.random.rand(3), dtype=tf.float32)
+lr = tf.constant(0.01, dtype=tf.float32)
+epsilon = tf.constant(1e-7, dtype=tf.float32)
+grad = tf.constant(np.array([0.5, 0.3, 0.2]), dtype=tf.float32)
+use_locking = False
+update_slots = True
+name = "test"
+casted_lr = tf.cast(lr, dtype=tf.float64)
+casted_epsilon = tf.cast(epsilon, dtype=tf.float64)
+casted_grad = tf.cast(grad, dtype=tf.float64)
+tf.raw_ops.ResourceApplyAdagradV2(
+    var=var.handle,
+    accum=accum.handle,
+    lr=casted_lr,
+    epsilon=casted_epsilon,
+    grad=casted_grad,
+    use_locking=use_locking,
+    update_slots=update_slots,
+    name=name
+)</t>
+  </si>
+  <si>
+    <t>The Tsplits parameter is passed as a TensorFlow dtype object (e.g., tf.int32) instead of a tensor containing split indices. The C++ kernel expects the tensor to have int64_t dtype, but the Python API incorrectly allows passing a dtype object, triggering a type mismatch during internal validation (int32 expected, got int64). Reproduced on multi-GPU setups with CUDA 11.x and Python 3.10.</t>
+  </si>
+  <si>
+    <t>Maintainers acknowledged the issue and marked it for community contributions. One maintainer noted that the Python API is correct but the C++ kernel has a type-mapping mismatch, expecting int64_t for the offsets tensor, and confirmed they are looking into it with a PR forthcoming.</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.17.0</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+input_data = tf.constant([b"hello", b"world"], dtype=tf.string)
+input_encoding = "UTF-8"
+errors = "strict"
+replacement_char = 65533
+replace_control_characters = False
+Tsplits = tf.int32  # Incorrect: passing dtype object instead of tensor
+name = None
+result = tf.raw_ops.UnicodeDecodeWithOffsets(
+    input=input_data,
+    input_encoding=input_encoding,
+    errors=errors,
+    replacement_char=replacement_char,
+    replace_control_characters=replace_control_characters,
+    Tsplits=Tsplits,
+    name=name
+)
+# Expected: Should accept tensor of split indices with dtype tf.int64
+# Actual: Core dump with 'int32 expected, got int64' due to type mismatch</t>
+  </si>
+  <si>
+    <t>Input tensor 'index' is 1D with shape [5], 'tf.expand_dims(result, 1)' creates a 2D index tensor of shape [5, 1], and 'tf.tensor_scatter_nd_update' is called with this 2D indices tensor on a 1D target tensor, causing a dimension bounds check failure (d &lt; dims()) where d=1 and dims()=1. Occurs in multi-GPU environment but root cause is dimension mismatch in scatter operation.</t>
+  </si>
+  <si>
+    <t>Maintainers acknowledged the issue and marked it as 'contribution welcome'. They stated the request is not currently prioritized and invited community contributions. They provided a Colab gist confirming reproduction on TF 2.19.0 and 2.20.0 and encouraged users to submit PRs with links to this issue.</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.17, 2.19.0, 2.20.0</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+index = tf.constant([0, 1, 2, 3, 4], dtype=tf.int32)
+seed = tf.constant([123, 456], dtype=tf.int32)
+tf.random.set_seed(seed[0])
+result = tf.random.shuffle(index, seed=seed[1])
+shuffled_indices = tf.tensor_scatter_nd_update(index, tf.expand_dims(result, 1), tf.range(tf.size(index)))
+# Expected: successful update
+# Actual: Crash with 'Check failed: d &lt; dims() (1 vs. 1)'</t>
+  </si>
+  <si>
+    <t>Passing permutation values of 9223372036854775807 (INT64_MAX) with a 4x4 sparse matrix, where permutation tensor is of type int32 and contains out-of-range indices exceeding the matrix dimensions. The permutation vector must contain integers {0, 1, ..., N-1} exactly once, but extreme values cause heap corruption.</t>
+  </si>
+  <si>
+    <t>The maintainer acknowledged that the permutation values provided are invalid, noting that the permutation vector must be of type int32 and contain integers {0, 1, ..., N-1} exactly once. They confirmed that the issue does not occur with valid inputs and provided a working gist with correct permutation values. No fix was implemented because the bug is due to invalid user input, not a code defect.</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+a_indices = tf.constant([[0, 0], [1, 1], [2, 1], [2, 2], [3, 3]], dtype=tf.int64)
+a_values = tf.constant([1.0, 2.0, 1.0, 3.0, 4.0], dtype=tf.float32)
+a_dense_shape = tf.constant([4, 4], dtype=tf.int64)
+a_st = tf.sparse.SparseTensor(a_indices, a_values, a_dense_shape)
+a_sm = tf.sparse.reorder(a_st)
+a_sm = tf.sparse.to_dense(a_sm)
+a_sm = tf.compat.v1.raw_ops.SparseTensorToCSRSparseMatrix(indices=a_indices, values=a_values, dense_shape=a_dense_shape)
+permutation = tf.constant([9223372036854775807, 9223372036854775807, 9223372036854775807, 9223372036854775807], dtype=tf.int32)
+result = tf.compat.v1.raw_ops.SparseMatrixSparseCholesky(input=a_sm, permutation=permutation, type=tf.float32, name='sparse_cholesky')
+# Expected: Proper validation and error message
+# Actual: 'double free or corruption (out)' followed by abort</t>
+  </si>
+  <si>
+    <t>Using batch_size=9223372036854775807 (INT64_MAX) with drop_remainder=True in tf.data.Dataset.batch(), triggering integer overflow in tensor shape calculation, leading to negative new_num_elements and fatal assertion failure in tensor_shape.cc. Occurs on CPU/GPU with any Python version and OS.</t>
+  </si>
+  <si>
+    <t>Maintainer acknowledged the crash and confirmed it reproduces in TensorFlow 2.20. They noted that the issue stems from lack of input validation and suggested manually ensuring batch_size is less than 2^63-1. No fix was committed, and the issue was closed due to inactivity.</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+data = [[1, 2, 3], [4, 5, 6], [7, 8, 9], [10, 11, 12]]
+dataset = tf.data.Dataset.from_tensor_slices(data)
+batched_dataset = dataset.batch(batch_size=9223372036854775807, drop_remainder=True, num_parallel_calls=tf.data.AUTOTUNE, deterministic=True, name='batched_dataset')
+# Expected: ValueError for invalid batch_size
+# Actual: Core dump with fatal assertion: Check failed: 0 &lt;= new_num_elements (0 vs. -1)</t>
+  </si>
+  <si>
+    <t>Calling tf.signal.rfft2d with a name parameter containing special characters (e.g., 'txt') on a GPU-enabled system, triggering CUDA device context initialization failure due to improper string handling during StreamExecutor initialization. The crash occurs before FFT computation, during GPU context acquisition, with CUDA_ERROR_OUT_OF_MEMORY despite sufficient memory.</t>
+  </si>
+  <si>
+    <t>A maintainer tested the issue on TensorFlow 2.20.0 nightly and could not reproduce the crash, indicating the issue may have been resolved in later versions. They provided a Colab gist as evidence and asked the reporter to confirm if the issue persists.</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+input_data = tf.random.uniform(shape=[10, 10], minval=0, maxval=1, dtype=tf.float32)
+fft_length = tf.constant([10, 10], dtype=tf.int32)
+result = tf.signal.rfft2d(input_tensor=input_data, fft_length=fft_length, name='txt')</t>
+  </si>
+  <si>
+    <t>CUDA_ERROR_INVALID_HANDLE and failed cuSolverDN instance creation when using tf.linalg.lu_solve with specific tensor inputs (lower_upper=[[3.0,1.0],[0.0,2.0]], perm=[0,0], rhs=[[1.0,0.0],[0.0,1.0]]), likely triggered by incompatible CUDA/cuDNN versions or GPU environment misconfiguration. The issue occurred on a local system with unreported CUDA/cuDNN/GPU details.</t>
+  </si>
+  <si>
+    <t>A maintainer (Kayyuri) tested the provided code in Google Colab with TensorFlow 2.17 and 2.21.0rc0 and could not reproduce the issue, suggesting the problem was due to incompatible CUDA/cuDNN versions on the reporter's system. They directed the user to official build configuration documentation and provided a working Colab gist.</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+lower_upper = tf.constant([[3.0, 1.0], [0.0, 2.0]], dtype=tf.float32)
+perm = tf.constant([0, 0], dtype=tf.int32)
+rhs = tf.constant([[1.0, 0.0], [0.0, 1.0]], dtype=tf.float32)
+solution = tf.linalg.lu_solve(lower_upper, perm, rhs, validate_args=True, name='solve_linear_eqn')</t>
+  </si>
+  <si>
+    <t>Using tf.map_fn with parallel_iterations &gt; 1 in eager execution mode on a GPU, particularly in multi-GPU environments. The bug triggers due to CUDA memory allocation failures, invalid resource handles during GPU-to-CPU memcpy, and stream synchronization issues. The error occurs despite small memory requests and is exacerbated by improper handling of CUDA streams and events in eager mode.</t>
+  </si>
+  <si>
+    <t>A maintainer tested the issue with TensorFlow 2.20.0 on GPU and confirmed the bug no longer reproduces, providing a Colab gist showing expected output. They noted that parallel_iterations &gt; 1 has no effect in eager mode and suggested using tf.function for parallel execution, implying the issue was resolved in later versions.</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+input_data = tf.constant([1, 2, 3, 4, 5])
+def square(x):
+    return x * x
+result = tf.map_fn(fn=square, elems=input_data, dtype=tf.int32,
+    parallel_iterations=10, back_prop=True, swap_memory=False, infer_shape=True, name='map_fn_example', fn_output_signature=tf.int32)
+print(result)</t>
+  </si>
+  <si>
+    <t>Processing a 1D tensor with extreme integer value 36028797018963968 using tf.reduce_min with axis=1 (invalid axis for 1D tensor), on a multi-GPU CUDA system. The crash occurs during CUDA device context initialization due to out-of-memory error, potentially triggered by improper tensor shape handling or memory allocation during reduction.</t>
+  </si>
+  <si>
+    <t>A maintainer noted that the provided code uses axis=1 on a 1D tensor, which is invalid and should raise an InvalidArgumentError. When corrected to axis=0, the code runs without issue on TensorFlow 2.20. No further analysis of the underlying CUDA context crash was provided.</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+input_tensor = tf.constant([36028797018963968, 36028797018963968])
+result = tf.reduce_min(input_tensor, axis=1, keepdims=True, name='reduce_min_op')</t>
+  </si>
+  <si>
+    <t>Passing a negative integer value (e.g., k=-1) as the k parameter to tf.raw_ops.NearestNeighbors with valid points and centers tensors on Ubuntu 22.04 with Python 3.10 and CUDA 12.4. The crash occurs due to internal shape validation rejecting negative dimensions, leading to an Aborted (core dumped) error.</t>
+  </si>
+  <si>
+    <t>The maintainer acknowledged the issue, confirmed that k must be a positive integer (≥1), and verified that the crash occurs due to invalid tensor shape generation. They provided a working example with k=1 and linked a Colab gist demonstrating correct behavior. No fix was implemented as the behavior was deemed correct by design — invalid inputs should fail, but the error message was misleading.</t>
+  </si>
+  <si>
+    <t>2025-10-24</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.18</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+points = tf.constant([[1.0, 2.0], [3.0, 4.0]], dtype=tf.float32)
+centers = tf.constant([[0.0, 0.0], [5.0, 5.0]], dtype=tf.float32)
+k = tf.constant(-1, dtype=tf.int64)
+result = tf.raw_ops.NearestNeighbors(points=points, centers=centers, k=k, name='NearestNeighbors')</t>
+  </si>
+  <si>
+    <t>The scores tensor has shape [2] instead of the required [batch_size, num_boxes, num_classes] = [2, 3, 2]. This mismatch triggers a failed assertion in tensor_shape.cc:357 (d &lt; dims()) leading to a core dump. The bug is triggered on CPU with TensorFlow 2.18.1 on Ubuntu 22.04. The input boxes tensor is correctly shaped as [2, 3, 2, 4].</t>
+  </si>
+  <si>
+    <t>The maintainer acknowledged that the crash was caused by an incorrect scores tensor shape, stating that the scores tensor must have shape [batch_size, num_boxes, num_classes] as per the documentation. They provided a working Colab gist with the correct shape and confirmed the function works when used properly.</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.18.1</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+print(tf.__version__)
+batch_size = 2
+num_boxes = 3
+num_classes = 2
+boxes = tf.constant([[[[0.0, 0.0, 1.0, 1.0], [0.0, 0.0, 0.5, 0.5]], [[0.5, 0.5, 1.0, 1.0], [0.6, 0.6, 1.0, 1.0]], [[0.1, 0.1, 0.4, 0.4], [0.2, 0.2, 0.3, 0.3]]], [[[0.0, 0.0, 1.0, 1.0], [0.0, 0.0, 0.5, 0.5]], [[0.5, 0.5, 1.0, 1.0], [0.6, 0.6, 1.0, 1.0]], [[0.1, 0.1, 0.4, 0.4], [0.2, 0.2, 0.3, 0.3]]]], dtype=tf.float32)
+scores = tf.constant([1, 1], dtype=tf.float32)  # Incorrect shape: [2] instead of [2, 3, 2]
+max_output_size_per_class = 2
+max_total_size = 3
+iou_threshold = 0.5
+score_threshold = -float('inf')
+pad_per_class = False
+clip_boxes = True
+name = 'nms'
+nmsed_boxes, nmsed_scores, nmsed_classes, valid_detections = tf.image.combined_non_max_suppression(boxes, scores, max_output_size_per_class, max_total_size, iou_threshold, score_threshold, pad_per_class, clip_boxes, name)</t>
+  </si>
+  <si>
+    <t>Using XLA compilation (@tf.function(jit_compile=True)), slicing the result of tf.where with negative start index [-1, 0] and end index [0, 3] on a 1D boolean input array. The crash occurs during tf.strided_slice execution. Bug does not occur in eager mode.</t>
+  </si>
+  <si>
+    <t>Maintainer confirmed reproduction on Colab with TF v2.21.0 and TF-nightly, noted that the issue does not occur in eager mode. No further analysis or fix details were provided in comments.</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.22.0-dev20260302</t>
+  </si>
+  <si>
+    <t>import numpy as np
+import tensorflow as tf
+class Model(tf.keras.Model):
+    def __init__(self):
+        super().__init__()
+    @tf.function(jit_compile=True)
+    def call(self, inputs, training=False):
+        result = tf.where(inputs)
+        result = tf.strided_slice(result, [-1, 0], [0, 3])
+        return result
+model = Model()
+inp = np.array([True, False, True], dtype=bool)
+model(inp, training=False)</t>
+  </si>
+  <si>
+    <t>Called with mismatched tensor shapes: gradient tensor has shape [10] while variable and accumulator have shape [6, 6], and indices tensor has 8 elements. Uses bfloat16 dtype, with use_locking=True and use_nesterov=True. Occurs on Linux platform. Shape validation fails in tensor_shape.cc:359 during SparseApplyMomentumOp::Compute.</t>
+  </si>
+  <si>
+    <t>Acknowledged the issue and confirmed reproduction on TensorFlow 2.19.0 and nightly. Marked as not prioritized and opened for community contributions. Asked contributors to fork the repo and submit a PR with a link to this issue.</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.19.0, TensorFlow 2.20.0-dev20250516</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+import numpy as np
+var = tf.Variable(np.random.random((6, 6)).astype(np.float32), dtype=tf.bfloat16)
+accum = tf.Variable(np.zeros((6, 6)).astype(np.float32), dtype=tf.bfloat16)
+lr_tensor = tf.constant(0.0, dtype=tf.bfloat16)
+grad_tensor = tf.constant(np.zeros(10), dtype=tf.bfloat16)
+indices_tensor = tf.constant([0, 0, 0, 1, 1, 2, 3, 4], dtype=tf.int32)
+momentum_tensor = tf.constant(0.9, dtype=tf.bfloat16)
+result = tf.raw_ops.ResourceSparseApplyMomentum(
+    var=var.handle,
+    accum=accum.handle,
+    lr=lr_tensor,
+    grad=grad_tensor,
+    indices=indices_tensor,
+    momentum=momentum_tensor,
+    use_locking=True,
+    use_nesterov=True
+)
+# Expected: Proper error or no crash
+# Actual: Segmentation fault with Check failed: d &lt; dims() (1 vs. 1)</t>
+  </si>
+  <si>
+    <t>Using a negative axis value (e.g., axis=-2) with tf.raw_ops.QuantizeAndDequantizeV3 on CPU with TensorFlow 2.19.0 or 2.20.0-dev20250516, involving float64 input tensor with extreme values, range_given=True, and narrow_range=True. The crash occurs due to an assertion failure in tensor_shape.cc when validating axis dimensions.</t>
+  </si>
+  <si>
+    <t>The maintainer acknowledged the issue, confirmed reproduction on multiple versions, and marked it as not prioritized for internal development. They suggested community contributions and later closed the issue due to inactivity, recommending users try the latest TensorFlow version and open a new issue if the problem persists.</t>
+  </si>
+  <si>
+    <t>2025-05-27</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.19.0, 2.20.0-dev20250516</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+import numpy as np
+input_tensor = tf.constant([
+    [[4.3136053036349129e-244, 1.2524328545813582e-21, 7.71590127777328e+26, 1.0, 2.0, 3.0],
+     [1e-100, 1e+100, -1e+50, 4.0, 5.0, 6.0]]
+], dtype=tf.float64)
+input_min = tf.constant(-5.4785109376353583e-282, dtype=tf.float64)
+input_max = tf.constant(1.4455588399771524e+73, dtype=tf.float64)
+num_bits = tf.constant(2, dtype=tf.int32)
+result = tf.raw_ops.QuantizeAndDequantizeV3(
+    input=input_tensor,
+    input_min=input_min,
+    input_max=input_max,
+    num_bits=num_bits,
+    signed_input=False,
+    range_given=True,
+    narrow_range=True,
+    axis=-2
+)</t>
+  </si>
+  <si>
+    <t>Crash occurs when input boundary values are passed to tf.config.threading.set_inter_op_parallelism_threads on Linux Ubuntu 22.04.3 LTS (x86_64) with Python 3.9.13, using GPU (NVIDIA GeForce RTX 4090). The exact boundary values are not specified, but the issue is triggered by invalid or extreme integer inputs to the function.</t>
+  </si>
+  <si>
+    <t>Maintainers acknowledged the issue and confirmed reproduction on TensorFlow 2.17 and tf-nightly. They marked it as 'contribution welcome' and stated it is not currently prioritized, inviting community contributions to fix it. No assignee or timeline was provided.</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+tf.config.threading.set_inter_op_parallelism_threads(-1)  # or other boundary value like 0 or very large number
+# This triggers segmentation fault on Linux with TensorFlow 2.17
+# Expected: No crash, valid input handling
+# Actual: Segmentation fault (core dumped)</t>
+  </si>
+  <si>
+    <t>When seq_len_max is set to a value greater than the time dimension of the input tensor x (e.g., x has time dimension 2 but seq_len_max=3), causing a failed assertion in tensor.cc:1078 with 'Check failed: limit &lt;= dim0_size'. Occurs on CPU/GPU with TensorFlow 2.19, reproducible in Colab.</t>
+  </si>
+  <si>
+    <t>dhantule confirmed the issue and reproduced the crash, noting that the process crashes the Colab session. They provided a workaround by deriving seq_len_max from the input tensor's time dimension and suggested the fix should implement proper exception handling instead of crashing.</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.19</t>
+  </si>
+  <si>
+    <t>import tensorflow as tf
+import numpy as np
+seq_len_max = 3
+batch_size = 2
+input_size = 4
+num_units = 5
+x = tf.constant(np.random.randn(seq_len_max - 1, batch_size, input_size).astype(np.float32)) # time dimension = 2
+cs_prev = tf.constant(np.random.randn(batch_size, num_units).astype(np.float32))
+h_prev = tf.constant(np.random.randn(batch_size, num_units).astype(np.float32))
+w = tf.constant(np.random.randn(input_size + num_units, 4 * num_units).astype(np.float32))
+wci = tf.constant(np.random.randn(num_units).astype(np.float32))
+wcf = tf.constant(np.random.randn(num_units).astype(np.float32))
+wco = tf.constant(np.random.randn(num_units).astype(np.float32))
+b = tf.constant(np.random.randn(4 * num_units).astype(np.float32))
+i = tf.constant(np.random.randn(seq_len_max - 1, batch_size, num_units).astype(np.float32))
+cs = tf.constant(np.random.randn(seq_len_max - 1, batch_size, num_units).astype(np.float32))
+f = tf.constant(np.random.randn(seq_len_max - 1, batch_size, num_units).astype(np.float32))
+o = tf.constant(np.random.randn(seq_len_max - 1, batch_size, num_units).astype(np.float32))
+ci = tf.constant(np.random.randn(seq_len_max - 1, batch_size, num_units).astype(np.float32))
+co = tf.constant(np.random.randn(seq_len_max - 1, batch_size, num_units).astype(np.float32))
+h = tf.constant(np.random.randn(seq_len_max - 1, batch_size, num_units).astype(np.float32))
+cs_grad = tf.constant(np.random.randn(seq_len_max - 1, batch_size, num_units).astype(np.float32))
+h_grad = tf.constant(np.random.randn(seq_len_max - 1, batch_size, num_units).astype(np.float32))
+use_peephole = True
+result = tf.raw_ops.BlockLSTMGradV2(
+    seq_len_max=seq_len_max,
+    x=x,
+    cs_prev=cs_prev,
+    h_prev=h_prev,
+    w=w,
+    wci=wci,
+    wcf=wcf,
+    wco=wco,
+    b=b,
+    i=i,
+    cs=cs,
+    f=f,
+    o=o,
+    ci=ci,
+    co=co,
+    h=h,
+    cs_grad=cs_grad,
+    h_grad=h_grad,
+    use_peephole=use_peephole
+)
+# Expected: Python exception (e.g., ValueError) for invalid seq_len_max
+# Actual: Segmentation fault / process crash with 'Check failed: limit &lt;= dim0_size (3 vs. 2)'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -458,6 +1071,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -467,7 +1092,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -489,12 +1114,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -506,6 +1146,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -825,64 +1480,84 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:T200"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:T201"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="2" max="2" width="47.42578125" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="48.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="346.5">
       <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -893,26 +1568,40 @@
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="379.5">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="F3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -923,26 +1612,40 @@
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ht="409.5">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>94</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -953,26 +1656,40 @@
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" ht="409.5">
       <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -983,26 +1700,40 @@
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" ht="379.5">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>101</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -1013,26 +1744,40 @@
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ht="409.5">
       <c r="A7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>105</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -1043,26 +1788,40 @@
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="409.5">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1073,26 +1832,38 @@
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="409.5">
       <c r="A9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
+      <c r="F9" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>113</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -1103,26 +1874,38 @@
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="379.5">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="F10" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>116</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -1133,26 +1916,38 @@
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="409.5">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+      <c r="F11" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -1163,26 +1958,38 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>34</v>
+    <row r="12" spans="1:20" ht="409.5">
+      <c r="A12" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="F12" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -1193,26 +2000,40 @@
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>35</v>
+    <row r="13" spans="1:20" ht="409.5">
+      <c r="A13" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -1223,26 +2044,38 @@
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="409.5">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="F14" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>132</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -1253,26 +2086,38 @@
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ht="409.5">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="F15" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>136</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1283,26 +2128,38 @@
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" ht="409.5">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
+      <c r="F16" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>139</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -1313,26 +2170,38 @@
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" ht="409.5">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
+      <c r="F17" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>143</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -1343,26 +2212,38 @@
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" ht="409.5">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
+      <c r="F18" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>147</v>
+      </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -1373,26 +2254,38 @@
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" ht="409.5">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="F19" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>151</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -1403,26 +2296,38 @@
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" ht="409.5">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
+      <c r="F20" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>154</v>
+      </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -1433,26 +2338,38 @@
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" ht="409.5">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="F21" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>159</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -1463,26 +2380,38 @@
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" ht="409.5">
       <c r="A22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
+      <c r="F22" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -1493,26 +2422,38 @@
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" ht="409.5">
       <c r="A23" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
+      <c r="F23" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>169</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -1523,26 +2464,38 @@
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" ht="409.5">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
+      <c r="F24" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>174</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -1553,26 +2506,38 @@
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" ht="409.5">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="F25" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>179</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -1583,26 +2548,38 @@
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" ht="409.5">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="F26" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>183</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -1613,18 +2590,38 @@
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+    <row r="27" spans="1:20" ht="409.5">
+      <c r="A27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="F27" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>188</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -1635,7 +2632,7 @@
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1657,7 +2654,7 @@
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1679,7 +2676,7 @@
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1701,7 +2698,7 @@
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1723,7 +2720,7 @@
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1745,7 +2742,7 @@
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1767,7 +2764,7 @@
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1789,7 +2786,7 @@
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1811,7 +2808,7 @@
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:20">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1833,7 +2830,7 @@
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1855,7 +2852,7 @@
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:20">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1877,7 +2874,7 @@
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:20">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1899,7 +2896,7 @@
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:20">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1921,7 +2918,7 @@
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:20">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1943,7 +2940,7 @@
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:20">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1965,7 +2962,7 @@
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:20">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1987,7 +2984,7 @@
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:20">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2009,7 +3006,7 @@
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:20">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2031,7 +3028,7 @@
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2053,7 +3050,7 @@
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:20">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2075,7 +3072,7 @@
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:20">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2097,7 +3094,7 @@
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:20">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2119,7 +3116,7 @@
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:20">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2141,7 +3138,7 @@
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:20">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2163,7 +3160,7 @@
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:20">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2185,7 +3182,7 @@
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:20">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2207,7 +3204,7 @@
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:20">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2229,7 +3226,7 @@
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:20">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2251,7 +3248,7 @@
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:20">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2273,7 +3270,7 @@
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:20">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2295,7 +3292,7 @@
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:20">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2317,7 +3314,7 @@
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:20">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2339,7 +3336,7 @@
       <c r="S59" s="1"/>
       <c r="T59" s="1"/>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:20">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2361,7 +3358,7 @@
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:20">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2383,7 +3380,7 @@
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:20">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2405,7 +3402,7 @@
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:20">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2427,7 +3424,7 @@
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:20">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2449,7 +3446,7 @@
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2471,7 +3468,7 @@
       <c r="S65" s="1"/>
       <c r="T65" s="1"/>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2493,7 +3490,7 @@
       <c r="S66" s="1"/>
       <c r="T66" s="1"/>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2515,7 +3512,7 @@
       <c r="S67" s="1"/>
       <c r="T67" s="1"/>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2537,7 +3534,7 @@
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2559,7 +3556,7 @@
       <c r="S69" s="1"/>
       <c r="T69" s="1"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2581,7 +3578,7 @@
       <c r="S70" s="1"/>
       <c r="T70" s="1"/>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2603,7 +3600,7 @@
       <c r="S71" s="1"/>
       <c r="T71" s="1"/>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2625,7 +3622,7 @@
       <c r="S72" s="1"/>
       <c r="T72" s="1"/>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2647,7 +3644,7 @@
       <c r="S73" s="1"/>
       <c r="T73" s="1"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2669,7 +3666,7 @@
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:20">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2691,7 +3688,7 @@
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:20">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2713,7 +3710,7 @@
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2735,7 +3732,7 @@
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2757,7 +3754,7 @@
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2779,7 +3776,7 @@
       <c r="S79" s="1"/>
       <c r="T79" s="1"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:20">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2801,7 +3798,7 @@
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:20">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2823,7 +3820,7 @@
       <c r="S81" s="1"/>
       <c r="T81" s="1"/>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:20">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2845,7 +3842,7 @@
       <c r="S82" s="1"/>
       <c r="T82" s="1"/>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:20">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2867,7 +3864,7 @@
       <c r="S83" s="1"/>
       <c r="T83" s="1"/>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:20">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2889,7 +3886,7 @@
       <c r="S84" s="1"/>
       <c r="T84" s="1"/>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:20">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2911,7 +3908,7 @@
       <c r="S85" s="1"/>
       <c r="T85" s="1"/>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:20">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2933,7 +3930,7 @@
       <c r="S86" s="1"/>
       <c r="T86" s="1"/>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:20">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2955,7 +3952,7 @@
       <c r="S87" s="1"/>
       <c r="T87" s="1"/>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:20">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2977,7 +3974,7 @@
       <c r="S88" s="1"/>
       <c r="T88" s="1"/>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:20">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2999,7 +3996,7 @@
       <c r="S89" s="1"/>
       <c r="T89" s="1"/>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:20">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3021,7 +4018,7 @@
       <c r="S90" s="1"/>
       <c r="T90" s="1"/>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:20">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3043,7 +4040,7 @@
       <c r="S91" s="1"/>
       <c r="T91" s="1"/>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:20">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3065,7 +4062,7 @@
       <c r="S92" s="1"/>
       <c r="T92" s="1"/>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:20">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3087,7 +4084,7 @@
       <c r="S93" s="1"/>
       <c r="T93" s="1"/>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:20">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3109,7 +4106,7 @@
       <c r="S94" s="1"/>
       <c r="T94" s="1"/>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:20">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3131,7 +4128,7 @@
       <c r="S95" s="1"/>
       <c r="T95" s="1"/>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:20">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3153,7 +4150,7 @@
       <c r="S96" s="1"/>
       <c r="T96" s="1"/>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:20">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3175,7 +4172,7 @@
       <c r="S97" s="1"/>
       <c r="T97" s="1"/>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:20">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3197,7 +4194,7 @@
       <c r="S98" s="1"/>
       <c r="T98" s="1"/>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:20">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3219,7 +4216,7 @@
       <c r="S99" s="1"/>
       <c r="T99" s="1"/>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:20">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3241,7 +4238,7 @@
       <c r="S100" s="1"/>
       <c r="T100" s="1"/>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:20">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3263,7 +4260,7 @@
       <c r="S101" s="1"/>
       <c r="T101" s="1"/>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:20">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3285,7 +4282,7 @@
       <c r="S102" s="1"/>
       <c r="T102" s="1"/>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:20">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3307,7 +4304,7 @@
       <c r="S103" s="1"/>
       <c r="T103" s="1"/>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:20">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3329,7 +4326,7 @@
       <c r="S104" s="1"/>
       <c r="T104" s="1"/>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:20">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3351,7 +4348,7 @@
       <c r="S105" s="1"/>
       <c r="T105" s="1"/>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:20">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3373,7 +4370,7 @@
       <c r="S106" s="1"/>
       <c r="T106" s="1"/>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:20">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3395,7 +4392,7 @@
       <c r="S107" s="1"/>
       <c r="T107" s="1"/>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:20">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3417,7 +4414,7 @@
       <c r="S108" s="1"/>
       <c r="T108" s="1"/>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:20">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3439,7 +4436,7 @@
       <c r="S109" s="1"/>
       <c r="T109" s="1"/>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:20">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3461,7 +4458,7 @@
       <c r="S110" s="1"/>
       <c r="T110" s="1"/>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:20">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3483,7 +4480,7 @@
       <c r="S111" s="1"/>
       <c r="T111" s="1"/>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:20">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3505,7 +4502,7 @@
       <c r="S112" s="1"/>
       <c r="T112" s="1"/>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:20">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3527,7 +4524,7 @@
       <c r="S113" s="1"/>
       <c r="T113" s="1"/>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:20">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3549,7 +4546,7 @@
       <c r="S114" s="1"/>
       <c r="T114" s="1"/>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:20">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3571,7 +4568,7 @@
       <c r="S115" s="1"/>
       <c r="T115" s="1"/>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:20">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3593,7 +4590,7 @@
       <c r="S116" s="1"/>
       <c r="T116" s="1"/>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:20">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3615,7 +4612,7 @@
       <c r="S117" s="1"/>
       <c r="T117" s="1"/>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:20">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3637,7 +4634,7 @@
       <c r="S118" s="1"/>
       <c r="T118" s="1"/>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:20">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3659,7 +4656,7 @@
       <c r="S119" s="1"/>
       <c r="T119" s="1"/>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:20">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3681,7 +4678,7 @@
       <c r="S120" s="1"/>
       <c r="T120" s="1"/>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:20">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3703,7 +4700,7 @@
       <c r="S121" s="1"/>
       <c r="T121" s="1"/>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:20">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3725,7 +4722,7 @@
       <c r="S122" s="1"/>
       <c r="T122" s="1"/>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:20">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3747,7 +4744,7 @@
       <c r="S123" s="1"/>
       <c r="T123" s="1"/>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:20">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3769,7 +4766,7 @@
       <c r="S124" s="1"/>
       <c r="T124" s="1"/>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:20">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3791,7 +4788,7 @@
       <c r="S125" s="1"/>
       <c r="T125" s="1"/>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:20">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3813,7 +4810,7 @@
       <c r="S126" s="1"/>
       <c r="T126" s="1"/>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:20">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -3835,7 +4832,7 @@
       <c r="S127" s="1"/>
       <c r="T127" s="1"/>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:20">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -3857,7 +4854,7 @@
       <c r="S128" s="1"/>
       <c r="T128" s="1"/>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:20">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -3879,7 +4876,7 @@
       <c r="S129" s="1"/>
       <c r="T129" s="1"/>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:20">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -3901,7 +4898,7 @@
       <c r="S130" s="1"/>
       <c r="T130" s="1"/>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:20">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -3923,7 +4920,7 @@
       <c r="S131" s="1"/>
       <c r="T131" s="1"/>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:20">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -3945,7 +4942,7 @@
       <c r="S132" s="1"/>
       <c r="T132" s="1"/>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:20">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -3967,7 +4964,7 @@
       <c r="S133" s="1"/>
       <c r="T133" s="1"/>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:20">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -3989,7 +4986,7 @@
       <c r="S134" s="1"/>
       <c r="T134" s="1"/>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:20">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4011,7 +5008,7 @@
       <c r="S135" s="1"/>
       <c r="T135" s="1"/>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:20">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4033,7 +5030,7 @@
       <c r="S136" s="1"/>
       <c r="T136" s="1"/>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:20">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4055,7 +5052,7 @@
       <c r="S137" s="1"/>
       <c r="T137" s="1"/>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:20">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4077,7 +5074,7 @@
       <c r="S138" s="1"/>
       <c r="T138" s="1"/>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:20">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4099,7 +5096,7 @@
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:20">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4121,7 +5118,7 @@
       <c r="S140" s="1"/>
       <c r="T140" s="1"/>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:20">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4143,7 +5140,7 @@
       <c r="S141" s="1"/>
       <c r="T141" s="1"/>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:20">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4165,7 +5162,7 @@
       <c r="S142" s="1"/>
       <c r="T142" s="1"/>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:20">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4187,7 +5184,7 @@
       <c r="S143" s="1"/>
       <c r="T143" s="1"/>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:20">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4209,7 +5206,7 @@
       <c r="S144" s="1"/>
       <c r="T144" s="1"/>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:20">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4231,7 +5228,7 @@
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:20">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4253,7 +5250,7 @@
       <c r="S146" s="1"/>
       <c r="T146" s="1"/>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:20">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4275,7 +5272,7 @@
       <c r="S147" s="1"/>
       <c r="T147" s="1"/>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:20">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4297,7 +5294,7 @@
       <c r="S148" s="1"/>
       <c r="T148" s="1"/>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:20">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4319,7 +5316,7 @@
       <c r="S149" s="1"/>
       <c r="T149" s="1"/>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:20">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4341,7 +5338,7 @@
       <c r="S150" s="1"/>
       <c r="T150" s="1"/>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:20">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4363,7 +5360,7 @@
       <c r="S151" s="1"/>
       <c r="T151" s="1"/>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:20">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4385,7 +5382,7 @@
       <c r="S152" s="1"/>
       <c r="T152" s="1"/>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:20">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4407,7 +5404,7 @@
       <c r="S153" s="1"/>
       <c r="T153" s="1"/>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:20">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4429,7 +5426,7 @@
       <c r="S154" s="1"/>
       <c r="T154" s="1"/>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:20">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4451,7 +5448,7 @@
       <c r="S155" s="1"/>
       <c r="T155" s="1"/>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:20">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4473,7 +5470,7 @@
       <c r="S156" s="1"/>
       <c r="T156" s="1"/>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:20">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4495,7 +5492,7 @@
       <c r="S157" s="1"/>
       <c r="T157" s="1"/>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:20">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4517,7 +5514,7 @@
       <c r="S158" s="1"/>
       <c r="T158" s="1"/>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:20">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4539,7 +5536,7 @@
       <c r="S159" s="1"/>
       <c r="T159" s="1"/>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:20">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4561,7 +5558,7 @@
       <c r="S160" s="1"/>
       <c r="T160" s="1"/>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:20">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4583,7 +5580,7 @@
       <c r="S161" s="1"/>
       <c r="T161" s="1"/>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:20">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4605,7 +5602,7 @@
       <c r="S162" s="1"/>
       <c r="T162" s="1"/>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:20">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4627,7 +5624,7 @@
       <c r="S163" s="1"/>
       <c r="T163" s="1"/>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:20">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4649,7 +5646,7 @@
       <c r="S164" s="1"/>
       <c r="T164" s="1"/>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:20">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4671,7 +5668,7 @@
       <c r="S165" s="1"/>
       <c r="T165" s="1"/>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:20">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -4693,7 +5690,7 @@
       <c r="S166" s="1"/>
       <c r="T166" s="1"/>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:20">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -4715,7 +5712,7 @@
       <c r="S167" s="1"/>
       <c r="T167" s="1"/>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:20">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -4737,7 +5734,7 @@
       <c r="S168" s="1"/>
       <c r="T168" s="1"/>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:20">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -4759,7 +5756,7 @@
       <c r="S169" s="1"/>
       <c r="T169" s="1"/>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:20">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -4781,7 +5778,7 @@
       <c r="S170" s="1"/>
       <c r="T170" s="1"/>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:20">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -4803,7 +5800,7 @@
       <c r="S171" s="1"/>
       <c r="T171" s="1"/>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:20">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -4825,7 +5822,7 @@
       <c r="S172" s="1"/>
       <c r="T172" s="1"/>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:20">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -4847,7 +5844,7 @@
       <c r="S173" s="1"/>
       <c r="T173" s="1"/>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:20">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -4869,7 +5866,7 @@
       <c r="S174" s="1"/>
       <c r="T174" s="1"/>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:20">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -4891,7 +5888,7 @@
       <c r="S175" s="1"/>
       <c r="T175" s="1"/>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:20">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -4913,7 +5910,7 @@
       <c r="S176" s="1"/>
       <c r="T176" s="1"/>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:20">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -4935,7 +5932,7 @@
       <c r="S177" s="1"/>
       <c r="T177" s="1"/>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:20">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -4957,7 +5954,7 @@
       <c r="S178" s="1"/>
       <c r="T178" s="1"/>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:20">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -4979,7 +5976,7 @@
       <c r="S179" s="1"/>
       <c r="T179" s="1"/>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:20">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5001,7 +5998,7 @@
       <c r="S180" s="1"/>
       <c r="T180" s="1"/>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:20">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5023,7 +6020,7 @@
       <c r="S181" s="1"/>
       <c r="T181" s="1"/>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:20">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5045,7 +6042,7 @@
       <c r="S182" s="1"/>
       <c r="T182" s="1"/>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:20">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5067,7 +6064,7 @@
       <c r="S183" s="1"/>
       <c r="T183" s="1"/>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:20">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5089,7 +6086,7 @@
       <c r="S184" s="1"/>
       <c r="T184" s="1"/>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:20">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5111,7 +6108,7 @@
       <c r="S185" s="1"/>
       <c r="T185" s="1"/>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:20">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5133,7 +6130,7 @@
       <c r="S186" s="1"/>
       <c r="T186" s="1"/>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:20">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5155,7 +6152,7 @@
       <c r="S187" s="1"/>
       <c r="T187" s="1"/>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:20">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5177,7 +6174,7 @@
       <c r="S188" s="1"/>
       <c r="T188" s="1"/>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:20">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5199,7 +6196,7 @@
       <c r="S189" s="1"/>
       <c r="T189" s="1"/>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:20">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5221,7 +6218,7 @@
       <c r="S190" s="1"/>
       <c r="T190" s="1"/>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:20">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5243,7 +6240,7 @@
       <c r="S191" s="1"/>
       <c r="T191" s="1"/>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:20">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -5265,7 +6262,7 @@
       <c r="S192" s="1"/>
       <c r="T192" s="1"/>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:20">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -5287,7 +6284,7 @@
       <c r="S193" s="1"/>
       <c r="T193" s="1"/>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:20">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -5309,7 +6306,7 @@
       <c r="S194" s="1"/>
       <c r="T194" s="1"/>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:20">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5331,7 +6328,7 @@
       <c r="S195" s="1"/>
       <c r="T195" s="1"/>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:20">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -5353,7 +6350,7 @@
       <c r="S196" s="1"/>
       <c r="T196" s="1"/>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:20">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5375,7 +6372,7 @@
       <c r="S197" s="1"/>
       <c r="T197" s="1"/>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:20">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -5397,7 +6394,7 @@
       <c r="S198" s="1"/>
       <c r="T198" s="1"/>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:20">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5419,7 +6416,7 @@
       <c r="S199" s="1"/>
       <c r="T199" s="1"/>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:20">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -5441,35 +6438,60 @@
       <c r="S200" s="1"/>
       <c r="T200" s="1"/>
     </row>
+    <row r="201" spans="1:20">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
+      <c r="E201" s="1"/>
+      <c r="F201" s="1"/>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1"/>
+      <c r="I201" s="1"/>
+      <c r="J201" s="1"/>
+      <c r="K201" s="1"/>
+      <c r="L201" s="1"/>
+      <c r="M201" s="1"/>
+      <c r="N201" s="1"/>
+      <c r="O201" s="1"/>
+      <c r="P201" s="1"/>
+      <c r="Q201" s="1"/>
+      <c r="R201" s="1"/>
+      <c r="S201" s="1"/>
+      <c r="T201" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B10" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="B16" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="B8" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="B3" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="B7" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="B11" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="B17" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="B15" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="B9" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="B2" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="B12" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="B21" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="B20" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="B1" r:id="rId16" display="https://github.com/CodersAcademy006/tensorflow/pull/9" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="B6" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="B18" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="B19" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="B14" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="B13" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="B22" r:id="rId22" xr:uid="{984C0341-9F5D-4527-9402-AEC1CF8C9E16}"/>
-    <hyperlink ref="B23" r:id="rId23" xr:uid="{ED7EA110-6DCF-4029-8BAA-79F01FD5045E}"/>
-    <hyperlink ref="B24" r:id="rId24" xr:uid="{8DEA114A-920D-4FE5-A3C6-8685FF0FBC91}"/>
-    <hyperlink ref="B25" r:id="rId25" xr:uid="{E9B9D026-AB54-4F8F-BDF9-52891F1EAB2A}"/>
-    <hyperlink ref="B26" r:id="rId26" xr:uid="{E0DA3264-7D45-4E5D-BA4C-E14B8DCE16B0}"/>
+    <hyperlink ref="B11" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="B9" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="B8" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="B12" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="B18" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="B16" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="B10" r:id="rId10" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="B3" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="B21" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="B2" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="B7" r:id="rId15" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="B19" r:id="rId16" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="B15" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="B14" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="B23" r:id="rId19" xr:uid="{984C0341-9F5D-4527-9402-AEC1CF8C9E16}"/>
+    <hyperlink ref="B24" r:id="rId20" xr:uid="{ED7EA110-6DCF-4029-8BAA-79F01FD5045E}"/>
+    <hyperlink ref="B25" r:id="rId21" xr:uid="{8DEA114A-920D-4FE5-A3C6-8685FF0FBC91}"/>
+    <hyperlink ref="B26" r:id="rId22" xr:uid="{E9B9D026-AB54-4F8F-BDF9-52891F1EAB2A}"/>
+    <hyperlink ref="B27" r:id="rId23" xr:uid="{E0DA3264-7D45-4E5D-BA4C-E14B8DCE16B0}"/>
+    <hyperlink ref="E7" r:id="rId24" xr:uid="{D1A2F6B2-CFD5-4BE1-AAD5-28CAE8903152}"/>
+    <hyperlink ref="E8" r:id="rId25" xr:uid="{9B6E89E9-CD76-4E3C-868E-D5D62395DA65}"/>
+    <hyperlink ref="E13" r:id="rId26" xr:uid="{E353BB5A-A66D-4A3C-9890-5849157DD36A}"/>
+    <hyperlink ref="B22" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="B20" r:id="rId28" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="B17" r:id="rId29" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
